--- a/input/mapping/064. OCB_GOLD_TCKH_CST_DIM_NEW_HOP.xlsx
+++ b/input/mapping/064. OCB_GOLD_TCKH_CST_DIM_NEW_HOP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1952" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49E6EF49-47ED-464C-9EA5-F5D6A007E224}"/>
+  <xr:revisionPtr revIDLastSave="1977" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC4D5DF5-9E36-4EF7-8D1E-1CF981DCB67F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2157" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="471">
   <si>
     <t>CST_DIM_NEW —  Data Lineage Summary</t>
   </si>
@@ -239,7 +239,16 @@
 -- CST_DIM_NEW  (Snapshot daily -&gt; INSERT REPLACE WHERE DATA_DT, idempotent)
 -- Nguồn: Silver (hub_customer, sts_hub_customer, sat_customer_*)
 -- Params: :cleaned, :curated, :DATADT (yyyyMMdd)
--- Nguồn Silver ở catalog :cleaned (khác default) -&gt; giữ IDENTIFIER
+-- Fix:
+--   2.4  : sat_customer_contact dùng &lt;= :DATADT (không phải = :DATADT)
+--   2.12 : sat_customer_contact snapshot 1 lần duy nhất -&gt; cte_contact
+--   X.11 : bỏ email_type_id / address_type_id / end_date (không tồn tại trong model)
+-- Trace DSX:
+--   ELC_ADR   = sat_customer_contact.email_1  (T24: T_EMAIL_1)
+--   CST_ADR   = sat_customer_contact.add_num  (T24: T_ADD_NUM)
+--   CST_FAX_NO= sat_customer_other.fax_1      (T24: T_FAX_1)
+--   CST_MBL_NO= NULL  (on-prem set_null())
+--   INN_BNKG_F= NULL  (on-prem set_null())
 -- =============================================================================
 CREATE TABLE IF NOT EXISTS CST_DIM_NEW (
     DATA_DT            DATE,
@@ -276,33 +285,23 @@
     GROUP BY customer_hashkey
     HAVING MAX_BY(cdc_status, source_event_date) = 'D'
 ),
--- Hub customer active
+-- ── Hub customer active
 cust_active AS (
     SELECT h.customer_hashkey, h.business_key
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_customer') h
-    LEFT JOIN sts_deleted d
-        ON h.customer_hashkey = d.customer_hashkey
+    LEFT JOIN sts_deleted d ON h.customer_hashkey = d.customer_hashkey
     WHERE d.customer_hashkey IS NULL
 ),
--- ── SQL1: ELC_ADR (sat_customer_contact -&gt; bảng đặc biệt: source_event_date = :DATADT)
-cte_elc AS (
+-- ── sat_customer_contact: snapshot 1 lần (fix 2.12), dùng &lt;= :DATADT (fix 2.4)
+--    Cột dùng: email_1-&gt;ELC_ADR, add_num-&gt;CST_ADR (fix X.11: bỏ email_type_id/address_type_id/end_date)
+--    CST_MBL_NO không lấy sms_1 vì on-prem set_null()
+cte_contact AS (
     SELECT
         customer_hashkey,
-        MAX_BY(email_1, source_event_date) AS ELC_ADR
+        MAX_BY(email_1, source_event_date) AS ELC_ADR,
+        MAX_BY(add_num,  source_event_date) AS CST_ADR
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_customer_contact')
-    WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
-      AND email_type_id IN (102200001, 102200002, 102200003, 102200005)
-    GROUP BY customer_hashkey
-),
--- ── SQL2: PST_ADR (sat_customer_contact -&gt; bảng đặc biệt: source_event_date = :DATADT)
-cte_pst AS (
-    SELECT
-        customer_hashkey,
-        MAX_BY(add_num, source_event_date) AS CST_ADR
-    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_customer_contact')
-    WHERE source_event_date = TO_DATE(:DATADT, 'yyyyMMdd')
-      AND address_type_id   = 104900001
-      AND end_date          = TO_DATE('20991231', 'yyyyMMdd')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
 ),
 -- ── Satellite information (bản mới nhất &lt;= :DATADT)
@@ -313,8 +312,7 @@
         MAX_BY(name_2,            source_event_date) AS name_2,
         MAX_BY(birth_incorp_date, source_event_date) AS birth_incorp_date,
         MAX_BY(gender,            source_event_date) AS gender,
-        MAX_BY(create_date,       source_event_date) AS create_date,
-        MAX(source_event_date)                       AS source_event_date
+        MAX_BY(create_date,       source_event_date) AS create_date
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_customer_information')
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
@@ -326,8 +324,7 @@
         MAX_BY(legal_id,       source_event_date) AS legal_id,
         MAX_BY(legal_doc_name, source_event_date) AS legal_doc_name,
         MAX_BY(legal_iss_date, source_event_date) AS legal_iss_date,
-        MAX_BY(tax_id,         source_event_date) AS tax_id,
-        MAX(source_event_date)                    AS source_event_date
+        MAX_BY(tax_id,         source_event_date) AS tax_id
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_customer_kyc')
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
@@ -337,61 +334,48 @@
     SELECT
         customer_hashkey,
         MAX_BY(cust_group,      source_event_date) AS cust_group,
-        MAX_BY(customer_status, source_event_date) AS customer_status,
-        MAX(source_event_date)                     AS source_event_date
+        MAX_BY(customer_status, source_event_date) AS customer_status
     FROM IDENTIFIER(:cleaned || '.raw_vault.sat_customer_classification')
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
 ),
--- ── SQL3: main query (CST INNER JOIN IP LEFT JOIN IDV LEFT JOIN ORG)
-cte_raw AS (
+-- ── Satellite other: fax_1-&gt;CST_FAX_NO (T24: T_FAX_1, bản mới nhất &lt;= :DATADT)
+sat_other AS (
     SELECT
-        h.customer_hashkey                                             AS CST_DW_ID,
-        CAST(h.business_key AS STRING)                                 AS UNQ_ID_SRC_STM,
-        TRIM(CONCAT(COALESCE(i.name_1,''),' ',COALESCE(i.name_2,''))) AS IP_NM,
-        TRIM(CONCAT(COALESCE(i.name_1,''),' ',COALESCE(i.name_2,''))) AS IP_FULL_NM,
-        TRY_TO_DATE(CAST(i.birth_incorp_date AS STRING),'yyyyMMdd')   AS BRTH_DT,
-        k.legal_id                                                     AS IDENTN_NO,
-        k.tax_id                                                       AS ORG_TAX_ID_NO,
-        CASE WHEN k.legal_doc_name = 'GPKD'
-             THEN k.legal_id ELSE NULL END                             AS ORG_TDG_LICENSE_ID,
-        TRY_TO_DATE(CAST(k.legal_iss_date AS STRING),'yyyyMMdd')      AS IDENTN_ISSU_DT,
-        i.gender                                                       AS GND_ID,
-        c.cust_group                                                   AS CST_GRP_ID,
-        CAST(c.customer_status AS STRING)                              AS CST_LCS_TP_ID,
-        TRY_TO_DATE(CAST(i.create_date AS STRING),'yyyyMMdd')         AS EFF_CST_DT,
-        CURRENT_TIMESTAMP()                                            AS CRT_TM,
-        CURRENT_TIMESTAMP()                                            AS PPN_TM
-    FROM cust_active h
-    LEFT JOIN sat_info i ON h.customer_hashkey = i.customer_hashkey
-    LEFT JOIN sat_kyc  k ON h.customer_hashkey = k.customer_hashkey
-    LEFT JOIN sat_cls  c ON h.customer_hashkey = c.customer_hashkey
+        customer_hashkey,
+        MAX_BY(fax_1, source_event_date) AS CST_FAX_NO
+    FROM IDENTIFIER(:cleaned || '.raw_vault.sat_customer_other')
+    WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
+    GROUP BY customer_hashkey
 )
 SELECT
-    TO_DATE(:DATADT, 'yyyyMMdd')  AS DATA_DT,
-    r.CST_DW_ID,
-    r.UNQ_ID_SRC_STM,
-    r.IP_NM,
-    r.IP_FULL_NM,
-    r.BRTH_DT,
-    r.IDENTN_NO,
-    r.ORG_TAX_ID_NO,
-    r.ORG_TDG_LICENSE_ID,
-    r.IDENTN_ISSU_DT,
-    r.GND_ID,
-    r.CST_GRP_ID,
-    r.CST_LCS_TP_ID,
-    r.EFF_CST_DT,
-    p.CST_ADR,
-    e.ELC_ADR,
-    NULL                    AS CST_FAX_NO,
-    NULL                    AS CST_MBL_NO,
-    NULL                    AS INN_BNKG_F,
-    r.CRT_TM,
-    r.PPN_TM
-FROM cte_raw r
-LEFT JOIN cte_pst p ON r.CST_DW_ID = p.customer_hashkey
-LEFT JOIN cte_elc e ON r.CST_DW_ID = e.customer_hashkey
+    TO_DATE(:DATADT, 'yyyyMMdd')                                           AS DATA_DT,
+    h.customer_hashkey                                                     AS CST_DW_ID,
+    CAST(h.business_key AS STRING)                                         AS UNQ_ID_SRC_STM,
+    TRIM(CONCAT(COALESCE(i.name_1,''),' ',COALESCE(i.name_2,'')))         AS IP_NM,
+    TRIM(CONCAT(COALESCE(i.name_1,''),' ',COALESCE(i.name_2,'')))         AS IP_FULL_NM,
+    TRY_TO_DATE(CAST(i.birth_incorp_date AS STRING), 'yyyyMMdd')          AS BRTH_DT,
+    k.legal_id                                                             AS IDENTN_NO,
+    k.tax_id                                                               AS ORG_TAX_ID_NO,
+    CASE WHEN k.legal_doc_name = 'GPKD' THEN k.legal_id ELSE NULL END     AS ORG_TDG_LICENSE_ID,
+    TRY_TO_DATE(CAST(k.legal_iss_date AS STRING), 'yyyyMMdd')             AS IDENTN_ISSU_DT,
+    i.gender                                                               AS GND_ID,
+    c.cust_group                                                           AS CST_GRP_ID,
+    CAST(c.customer_status AS STRING)                                      AS CST_LCS_TP_ID,
+    TRY_TO_DATE(CAST(i.create_date AS STRING), 'yyyyMMdd')                AS EFF_CST_DT,
+    ct.CST_ADR,
+    ct.ELC_ADR,
+    o.CST_FAX_NO,
+    NULL                                                                   AS CST_MBL_NO,
+    NULL                                                                   AS INN_BNKG_F,
+    CURRENT_TIMESTAMP()                                                    AS CRT_TM,
+    CURRENT_TIMESTAMP()                                                    AS PPN_TM
+FROM cust_active h
+LEFT JOIN sat_info    i  ON h.customer_hashkey = i.customer_hashkey
+LEFT JOIN sat_kyc     k  ON h.customer_hashkey = k.customer_hashkey
+LEFT JOIN sat_cls     c  ON h.customer_hashkey = c.customer_hashkey
+LEFT JOIN cte_contact ct ON h.customer_hashkey = ct.customer_hashkey
+LEFT JOIN sat_other   o  ON h.customer_hashkey = o.customer_hashkey
 ;</t>
   </si>
   <si>
@@ -1688,42 +1672,33 @@
 CTE FROM sat_customer_classification WHERE source_event_date &lt;= :DATADT GROUP BY customer_hashkey, lấy MAX_BY cho cust_group, customer_status</t>
   </si>
   <si>
-    <t>cte_pst (CTE)</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>LEFT JOIN (join với cte_raw r)</t>
-  </si>
-  <si>
-    <t>ON r.CST_DW_ID = p.customer_hashkey
-CTE FROM sat_customer_contact WHERE source_event_date = :DATADT (bằng đúng ngày) AND address_type_id=104900001 AND end_date=TO_DATE('20991231') GROUP BY customer_hashkey → MAX_BY(add_num) AS CST_ADR</t>
-  </si>
-  <si>
-    <t>cte_elc (CTE)</t>
-  </si>
-  <si>
-    <t>e</t>
-  </si>
-  <si>
-    <t>ON r.CST_DW_ID = e.customer_hashkey
-CTE FROM sat_customer_contact WHERE source_event_date = :DATADT AND email_type_id IN (102200001,102200002,102200003,102200005) GROUP BY customer_hashkey → MAX_BY(email_1) AS ELC_ADR</t>
+    <t>cte_contact (CTE)</t>
+  </si>
+  <si>
+    <t>ct</t>
+  </si>
+  <si>
+    <t>LEFT JOIN (join với h.customer_hashkey)</t>
+  </si>
+  <si>
+    <t>ON h.customer_hashkey = ct.customer_hashkey
+CTE cte_contact FROM sat_customer_contact WHERE source_event_date &lt;= :DATADT (fix: trước là = :DATADT) GROUP BY customer_hashkey → MAX_BY(email_1) AS ELC_ADR, MAX_BY(add_num) AS CST_ADR (fix: bỏ address_type_id/email_type_id/end_date filter — không tồn tại trong model)</t>
+  </si>
+  <si>
+    <t>sat_other (CTE)</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>ON h.customer_hashkey = o.customer_hashkey
+CTE sat_other FROM sat_customer_other WHERE source_event_date &lt;= :DATADT GROUP BY customer_hashkey → MAX_BY(fax_1) AS CST_FAX_NO</t>
   </si>
   <si>
     <t xml:space="preserve">                          </t>
   </si>
   <si>
-    <t>cte_raw (CTE)</t>
-  </si>
-  <si>
-    <t>r</t>
-  </si>
-  <si>
-    <t>BASE của SELECT cuối</t>
-  </si>
-  <si>
-    <t>Gộp cust_active + sat_info + sat_kyc + sat_cls, tạo sẵn các cột nghiệp vụ; SELECT cuối lấy FROM cte_raw r rồi LEFT JOIN cte_pst p và cte_elc e</t>
+    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>CST_DIM_NEW</t>
@@ -1810,19 +1785,19 @@
     <t>CST_ADR</t>
   </si>
   <si>
-    <t>p.CST_ADR</t>
+    <t>ct.CST_ADR</t>
   </si>
   <si>
     <t>ELC_ADR</t>
   </si>
   <si>
-    <t>e.ELC_ADR</t>
+    <t>ct.ELC_ADR</t>
   </si>
   <si>
     <t>CST_FAX_NO</t>
   </si>
   <si>
-    <t>NULL AS CST_FAX_NO</t>
+    <t>o.CST_FAX_NO</t>
   </si>
   <si>
     <t>CST_MBL_NO</t>
@@ -1844,9 +1819,6 @@
   </si>
   <si>
     <t>PPN_TM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -2683,7 +2655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="229">
+  <cellXfs count="228">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3069,202 +3041,7 @@
     <xf numFmtId="20" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3275,11 +3052,14 @@
     <xf numFmtId="0" fontId="41" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3287,17 +3067,208 @@
     <xf numFmtId="0" fontId="41" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3682,12 +3653,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:48" ht="30" customHeight="1">
-      <c r="A1" s="144" t="s">
+      <c r="A1" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="145"/>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
       <c r="E1" s="134"/>
       <c r="F1" s="134"/>
       <c r="G1" s="134"/>
@@ -3734,10 +3705,10 @@
       <c r="AV1" s="39"/>
     </row>
     <row r="2" spans="1:48" ht="76.5">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="153" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="143"/>
+      <c r="B2" s="153"/>
       <c r="C2" s="123" t="s">
         <v>2</v>
       </c>
@@ -3755,10 +3726,10 @@
       <c r="I3" s="131"/>
     </row>
     <row r="4" spans="1:48">
-      <c r="A4" s="146" t="s">
+      <c r="A4" s="156" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="147"/>
+      <c r="B4" s="157"/>
       <c r="C4" s="133"/>
       <c r="D4" s="131"/>
       <c r="E4" s="132"/>
@@ -3768,7 +3739,7 @@
     </row>
     <row r="5" spans="1:48" ht="18.75" customHeight="1">
       <c r="A5" s="117"/>
-      <c r="B5" s="219" t="s">
+      <c r="B5" s="218" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="133"/>
@@ -3780,7 +3751,7 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" s="118"/>
-      <c r="B6" s="219" t="s">
+      <c r="B6" s="218" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="133"/>
@@ -3792,7 +3763,7 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" s="119"/>
-      <c r="B7" s="219" t="s">
+      <c r="B7" s="218" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="125"/>
@@ -3804,7 +3775,7 @@
     </row>
     <row r="8" spans="1:48" ht="15.75" customHeight="1">
       <c r="A8" s="120"/>
-      <c r="B8" s="219" t="s">
+      <c r="B8" s="218" t="s">
         <v>8</v>
       </c>
       <c r="C8" s="125"/>
@@ -3814,7 +3785,7 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" s="121"/>
-      <c r="B9" s="219" t="s">
+      <c r="B9" s="218" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="125"/>
@@ -3843,10 +3814,10 @@
       <c r="H11" s="128"/>
     </row>
     <row r="12" spans="1:48">
-      <c r="A12" s="220" t="s">
+      <c r="A12" s="219" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="220" t="s">
+      <c r="B12" s="219" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="125"/>
@@ -3857,10 +3828,10 @@
     <row r="13" spans="1:48">
       <c r="A13" s="137"/>
       <c r="B13" s="137"/>
-      <c r="C13" s="219"/>
+      <c r="C13" s="218"/>
     </row>
     <row r="14" spans="1:48">
-      <c r="C14" s="219"/>
+      <c r="C14" s="218"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4103,13 +4074,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="191" t="s">
+      <c r="A1" s="201" t="s">
         <v>308</v>
       </c>
-      <c r="B1" s="192"/>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
-      <c r="E1" s="192"/>
+      <c r="B1" s="202"/>
+      <c r="C1" s="202"/>
+      <c r="D1" s="202"/>
+      <c r="E1" s="202"/>
     </row>
     <row r="2" spans="1:5" ht="18.75">
       <c r="A2" s="61" t="s">
@@ -4151,13 +4122,13 @@
       <c r="E4" s="63"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="192" t="s">
+      <c r="A5" s="202" t="s">
         <v>311</v>
       </c>
-      <c r="B5" s="192"/>
-      <c r="C5" s="192"/>
-      <c r="D5" s="192"/>
-      <c r="E5" s="192"/>
+      <c r="B5" s="202"/>
+      <c r="C5" s="202"/>
+      <c r="D5" s="202"/>
+      <c r="E5" s="202"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="61" t="s">
@@ -4290,14 +4261,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="203" t="s">
         <v>318</v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="194"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
+      <c r="B1" s="204"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="66" t="s">
@@ -4306,10 +4277,10 @@
       <c r="B2" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="195" t="s">
+      <c r="C2" s="205" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="196"/>
+      <c r="D2" s="206"/>
       <c r="E2" s="66" t="s">
         <v>25</v>
       </c>
@@ -4324,8 +4295,8 @@
       <c r="B3" s="68" t="s">
         <v>319</v>
       </c>
-      <c r="C3" s="197"/>
-      <c r="D3" s="198"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="208"/>
       <c r="E3" s="68" t="s">
         <v>29</v>
       </c>
@@ -4342,13 +4313,13 @@
       <c r="F4" s="69"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="194" t="s">
+      <c r="A5" s="204" t="s">
         <v>321</v>
       </c>
-      <c r="B5" s="194"/>
-      <c r="C5" s="194"/>
-      <c r="D5" s="194"/>
-      <c r="E5" s="194"/>
+      <c r="B5" s="204"/>
+      <c r="C5" s="204"/>
+      <c r="D5" s="204"/>
+      <c r="E5" s="204"/>
       <c r="F5" s="70"/>
     </row>
     <row r="6" spans="1:6">
@@ -5608,14 +5579,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="46.5" customHeight="1">
-      <c r="A1" s="199" t="s">
+      <c r="A1" s="209" t="s">
         <v>387</v>
       </c>
-      <c r="B1" s="200"/>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
     </row>
     <row r="2" spans="1:6" ht="18.75">
       <c r="A2" s="60" t="s">
@@ -5624,10 +5595,10 @@
       <c r="B2" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="200" t="s">
+      <c r="C2" s="210" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="200"/>
+      <c r="D2" s="210"/>
       <c r="E2" s="60" t="s">
         <v>25</v>
       </c>
@@ -5644,13 +5615,13 @@
       <c r="F3" s="75"/>
     </row>
     <row r="4" spans="1:6" ht="18.75">
-      <c r="A4" s="200" t="s">
+      <c r="A4" s="210" t="s">
         <v>388</v>
       </c>
-      <c r="B4" s="200"/>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="200"/>
+      <c r="B4" s="210"/>
+      <c r="C4" s="210"/>
+      <c r="D4" s="210"/>
+      <c r="E4" s="210"/>
       <c r="F4" s="76"/>
     </row>
     <row r="5" spans="1:6" ht="18.75">
@@ -6901,13 +6872,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="37.5" customHeight="1">
-      <c r="A1" s="201" t="s">
+      <c r="A1" s="211" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="202"/>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
+      <c r="B1" s="212"/>
+      <c r="C1" s="212"/>
+      <c r="D1" s="212"/>
+      <c r="E1" s="212"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="81" t="s">
@@ -6942,13 +6913,13 @@
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="203" t="s">
+      <c r="A4" s="213" t="s">
         <v>393</v>
       </c>
-      <c r="B4" s="204"/>
-      <c r="C4" s="204"/>
-      <c r="D4" s="204"/>
-      <c r="E4" s="205"/>
+      <c r="B4" s="214"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="215"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="81" t="s">
@@ -7064,13 +7035,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="47.25" customHeight="1">
-      <c r="A1" s="206" t="s">
+      <c r="A1" s="216" t="s">
         <v>397</v>
       </c>
-      <c r="B1" s="207"/>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="207"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="85" t="s">
@@ -7097,13 +7068,13 @@
       <c r="E3" s="86"/>
     </row>
     <row r="5" spans="1:5" ht="18.75">
-      <c r="A5" s="200" t="s">
+      <c r="A5" s="210" t="s">
         <v>398</v>
       </c>
-      <c r="B5" s="200"/>
-      <c r="C5" s="200"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="200"/>
+      <c r="B5" s="210"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="210"/>
+      <c r="E5" s="210"/>
     </row>
     <row r="6" spans="1:5" ht="18.75">
       <c r="A6" s="60" t="s">
@@ -7377,187 +7348,181 @@
       <c r="F1" s="138"/>
     </row>
     <row r="2" spans="1:10" s="140" customFormat="1">
-      <c r="A2" s="210" t="s">
+      <c r="A2" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="210" t="s">
+      <c r="B2" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="210" t="s">
+      <c r="C2" s="145" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="210" t="s">
+      <c r="D2" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="215" t="s">
+      <c r="E2" s="151" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="216"/>
+      <c r="F2" s="152"/>
     </row>
     <row r="3" spans="1:10" ht="39.75" customHeight="1">
-      <c r="A3" s="214">
+      <c r="A3" s="148">
         <v>1</v>
       </c>
-      <c r="B3" s="213" t="s">
+      <c r="B3" s="148" t="s">
         <v>407</v>
       </c>
-      <c r="C3" s="213" t="s">
+      <c r="C3" s="148" t="s">
         <v>310</v>
       </c>
-      <c r="D3" s="213" t="s">
+      <c r="D3" s="148" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="217" t="s">
+      <c r="E3" s="149" t="s">
         <v>408</v>
       </c>
-      <c r="F3" s="218"/>
-      <c r="G3" s="209"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="144"/>
     </row>
     <row r="4" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A4" s="214">
+      <c r="A4" s="148">
         <v>2</v>
       </c>
-      <c r="B4" s="213" t="s">
+      <c r="B4" s="148" t="s">
         <v>409</v>
       </c>
-      <c r="C4" s="213" t="s">
+      <c r="C4" s="148" t="s">
         <v>410</v>
       </c>
-      <c r="D4" s="213" t="s">
+      <c r="D4" s="148" t="s">
         <v>411</v>
       </c>
-      <c r="E4" s="217" t="s">
+      <c r="E4" s="149" t="s">
         <v>412</v>
       </c>
-      <c r="F4" s="218"/>
-      <c r="G4" s="209"/>
+      <c r="F4" s="150"/>
+      <c r="G4" s="144"/>
     </row>
     <row r="5" spans="1:10" ht="49.5" customHeight="1">
-      <c r="A5" s="214">
+      <c r="A5" s="148">
         <v>3</v>
       </c>
-      <c r="B5" s="213" t="s">
+      <c r="B5" s="148" t="s">
         <v>413</v>
       </c>
-      <c r="C5" s="213" t="s">
+      <c r="C5" s="148" t="s">
         <v>414</v>
       </c>
-      <c r="D5" s="213" t="s">
+      <c r="D5" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="217" t="s">
+      <c r="E5" s="149" t="s">
         <v>415</v>
       </c>
-      <c r="F5" s="218"/>
-      <c r="G5" s="209"/>
+      <c r="F5" s="150"/>
+      <c r="G5" s="144"/>
     </row>
     <row r="6" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A6" s="214">
+      <c r="A6" s="148">
         <v>4</v>
       </c>
-      <c r="B6" s="213" t="s">
+      <c r="B6" s="148" t="s">
         <v>416</v>
       </c>
-      <c r="C6" s="213" t="s">
+      <c r="C6" s="148" t="s">
         <v>417</v>
       </c>
-      <c r="D6" s="213" t="s">
+      <c r="D6" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="217" t="s">
+      <c r="E6" s="149" t="s">
         <v>418</v>
       </c>
-      <c r="F6" s="218"/>
-      <c r="G6" s="209"/>
+      <c r="F6" s="150"/>
+      <c r="G6" s="144"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="214">
+      <c r="A7" s="148">
         <v>5</v>
       </c>
-      <c r="B7" s="213" t="s">
+      <c r="B7" s="148" t="s">
         <v>419</v>
       </c>
-      <c r="C7" s="213" t="s">
+      <c r="C7" s="148" t="s">
         <v>420</v>
       </c>
-      <c r="D7" s="213" t="s">
+      <c r="D7" s="148" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="217" t="s">
+      <c r="E7" s="149" t="s">
         <v>421</v>
       </c>
-      <c r="F7" s="218"/>
-      <c r="G7" s="209"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="144"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="214">
+      <c r="A8" s="148">
         <v>6</v>
       </c>
-      <c r="B8" s="213" t="s">
+      <c r="B8" s="148" t="s">
         <v>422</v>
       </c>
-      <c r="C8" s="213" t="s">
+      <c r="C8" s="148" t="s">
         <v>423</v>
       </c>
-      <c r="D8" s="213" t="s">
+      <c r="D8" s="148" t="s">
         <v>424</v>
       </c>
-      <c r="E8" s="217" t="s">
+      <c r="E8" s="149" t="s">
         <v>425</v>
       </c>
-      <c r="F8" s="218"/>
-      <c r="G8" s="209"/>
+      <c r="F8" s="150"/>
+      <c r="G8" s="144"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="214">
+      <c r="A9" s="148">
         <v>7</v>
       </c>
-      <c r="B9" s="213" t="s">
+      <c r="B9" s="148" t="s">
         <v>426</v>
       </c>
-      <c r="C9" s="213" t="s">
+      <c r="C9" s="148" t="s">
         <v>427</v>
       </c>
-      <c r="D9" s="213" t="s">
+      <c r="D9" s="148" t="s">
         <v>424</v>
       </c>
-      <c r="E9" s="217" t="s">
+      <c r="E9" s="149" t="s">
         <v>428</v>
       </c>
-      <c r="F9" s="218"/>
-      <c r="G9" s="209"/>
+      <c r="F9" s="150"/>
+      <c r="G9" s="144"/>
       <c r="J9" s="4" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="214">
-        <v>8</v>
-      </c>
-      <c r="B10" s="213" t="s">
+      <c r="A10" s="148"/>
+      <c r="B10" s="148"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="148" t="s">
         <v>430</v>
       </c>
-      <c r="C10" s="213" t="s">
-        <v>431</v>
-      </c>
-      <c r="D10" s="213" t="s">
-        <v>432</v>
-      </c>
-      <c r="E10" s="217" t="s">
-        <v>433</v>
-      </c>
-      <c r="F10" s="218"/>
-      <c r="G10" s="209"/>
+      <c r="E10" s="149" t="s">
+        <v>430</v>
+      </c>
+      <c r="F10" s="150"/>
+      <c r="G10" s="144"/>
     </row>
     <row r="11" spans="1:10" s="140" customFormat="1">
-      <c r="A11" s="211" t="s">
+      <c r="A11" s="146" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="211"/>
-      <c r="C11" s="211"/>
-      <c r="D11" s="211"/>
-      <c r="E11" s="212"/>
-      <c r="F11" s="211"/>
+      <c r="B11" s="146"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="146"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="138" t="s">
@@ -7584,7 +7549,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C13" s="141" t="s">
         <v>182</v>
@@ -7592,11 +7557,11 @@
       <c r="D13" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="208" t="s">
+      <c r="E13" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F13" s="141" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -7604,10 +7569,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C14" s="141" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D14" s="141" t="s">
         <v>43</v>
@@ -7616,7 +7581,7 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="F14" s="141" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -7624,10 +7589,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C15" s="141" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D15" s="141" t="s">
         <v>43</v>
@@ -7636,7 +7601,7 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="F15" s="141" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -7644,19 +7609,19 @@
         <v>4</v>
       </c>
       <c r="B16" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C16" s="141" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D16" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="208" t="s">
+      <c r="E16" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F16" s="141" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -7664,19 +7629,19 @@
         <v>5</v>
       </c>
       <c r="B17" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C17" s="141" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D17" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="208" t="s">
+      <c r="E17" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F17" s="141" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -7684,19 +7649,19 @@
         <v>6</v>
       </c>
       <c r="B18" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C18" s="141" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D18" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="208" t="s">
+      <c r="E18" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F18" s="141" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="75" customHeight="1">
@@ -7704,10 +7669,10 @@
         <v>7</v>
       </c>
       <c r="B19" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C19" s="141" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D19" s="141" t="s">
         <v>43</v>
@@ -7716,7 +7681,7 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="F19" s="141" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="78.599999999999994" customHeight="1">
@@ -7724,10 +7689,10 @@
         <v>8</v>
       </c>
       <c r="B20" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C20" s="141" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D20" s="141" t="s">
         <v>43</v>
@@ -7736,7 +7701,7 @@
         <v>4.2361111111111113E-2</v>
       </c>
       <c r="F20" s="141" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -7744,19 +7709,19 @@
         <v>9</v>
       </c>
       <c r="B21" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C21" s="141" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D21" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="E21" s="208" t="s">
+      <c r="E21" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F21" s="141" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -7764,19 +7729,19 @@
         <v>10</v>
       </c>
       <c r="B22" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C22" s="141" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D22" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="208" t="s">
+      <c r="E22" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F22" s="141" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -7784,10 +7749,10 @@
         <v>11</v>
       </c>
       <c r="B23" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C23" s="141" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D23" s="141" t="s">
         <v>43</v>
@@ -7796,7 +7761,7 @@
         <v>4.2361111111111099E-2</v>
       </c>
       <c r="F23" s="141" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -7804,10 +7769,10 @@
         <v>12</v>
       </c>
       <c r="B24" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C24" s="141" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D24" s="141" t="s">
         <v>43</v>
@@ -7816,7 +7781,7 @@
         <v>4.2361111111111099E-2</v>
       </c>
       <c r="F24" s="141" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -7824,19 +7789,19 @@
         <v>13</v>
       </c>
       <c r="B25" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C25" s="141" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D25" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="208" t="s">
+      <c r="E25" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F25" s="141" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -7844,19 +7809,19 @@
         <v>14</v>
       </c>
       <c r="B26" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C26" s="141" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="D26" s="141" t="s">
         <v>58</v>
       </c>
-      <c r="E26" s="208" t="s">
+      <c r="E26" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F26" s="141" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -7864,10 +7829,10 @@
         <v>15</v>
       </c>
       <c r="B27" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C27" s="141" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D27" s="141" t="s">
         <v>43</v>
@@ -7876,7 +7841,7 @@
         <v>4.2361111111111099E-2</v>
       </c>
       <c r="F27" s="141" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -7884,10 +7849,10 @@
         <v>16</v>
       </c>
       <c r="B28" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C28" s="141" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D28" s="141" t="s">
         <v>43</v>
@@ -7896,7 +7861,7 @@
         <v>4.2361111111111099E-2</v>
       </c>
       <c r="F28" s="141" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -7904,19 +7869,19 @@
         <v>17</v>
       </c>
       <c r="B29" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C29" s="141" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D29" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="208" t="s">
+      <c r="E29" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F29" s="141" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -7924,19 +7889,19 @@
         <v>18</v>
       </c>
       <c r="B30" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C30" s="141" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D30" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="E30" s="208" t="s">
+      <c r="E30" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F30" s="141" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -7944,19 +7909,19 @@
         <v>19</v>
       </c>
       <c r="B31" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C31" s="141" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D31" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="E31" s="208" t="s">
+      <c r="E31" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F31" s="141" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -7964,19 +7929,19 @@
         <v>20</v>
       </c>
       <c r="B32" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C32" s="141" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D32" s="141" t="s">
         <v>325</v>
       </c>
-      <c r="E32" s="208" t="s">
+      <c r="E32" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F32" s="141" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -7984,24 +7949,24 @@
         <v>21</v>
       </c>
       <c r="B33" s="141" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C33" s="141" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D33" s="141" t="s">
         <v>325</v>
       </c>
-      <c r="E33" s="208" t="s">
+      <c r="E33" s="143" t="s">
         <v>226</v>
       </c>
       <c r="F33" s="141" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="F35" s="4" t="s">
-        <v>474</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -8060,7 +8025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="409.6">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -8068,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="33"/>
-      <c r="D3" s="221" t="s">
+      <c r="D3" s="220" t="s">
         <v>20</v>
       </c>
     </row>
@@ -8093,16 +8058,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="158" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="149"/>
-      <c r="C1" s="149"/>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
-      <c r="F1" s="149"/>
-      <c r="G1" s="150"/>
-      <c r="H1" s="222"/>
+      <c r="B1" s="159"/>
+      <c r="C1" s="159"/>
+      <c r="D1" s="159"/>
+      <c r="E1" s="159"/>
+      <c r="F1" s="159"/>
+      <c r="G1" s="160"/>
+      <c r="H1" s="221"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="93" t="s">
@@ -8117,12 +8082,12 @@
       <c r="D2" s="94" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="149" t="s">
+      <c r="E2" s="159" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="149"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="222"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="221"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="90">
@@ -8137,10 +8102,10 @@
       <c r="D3" s="91" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="152"/>
-      <c r="F3" s="152"/>
-      <c r="G3" s="153"/>
-      <c r="H3" s="222"/>
+      <c r="E3" s="162"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="221"/>
     </row>
     <row r="4" spans="1:8" ht="64.5" customHeight="1">
       <c r="A4" s="90">
@@ -8155,24 +8120,24 @@
       <c r="D4" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="152" t="s">
+      <c r="E4" s="162" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="152"/>
-      <c r="G4" s="153"/>
-      <c r="H4" s="222"/>
+      <c r="F4" s="162"/>
+      <c r="G4" s="163"/>
+      <c r="H4" s="221"/>
     </row>
     <row r="5" spans="1:8" ht="24.75" customHeight="1">
-      <c r="A5" s="154" t="s">
+      <c r="A5" s="164" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="155"/>
-      <c r="C5" s="155"/>
-      <c r="D5" s="155"/>
-      <c r="E5" s="155"/>
-      <c r="F5" s="155"/>
-      <c r="G5" s="156"/>
-      <c r="H5" s="222"/>
+      <c r="B5" s="165"/>
+      <c r="C5" s="165"/>
+      <c r="D5" s="165"/>
+      <c r="E5" s="165"/>
+      <c r="F5" s="165"/>
+      <c r="G5" s="166"/>
+      <c r="H5" s="221"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="93" t="s">
@@ -8196,7 +8161,7 @@
       <c r="G6" s="94" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="222"/>
+      <c r="H6" s="221"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="90">
@@ -8220,7 +8185,7 @@
       <c r="G7" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="222"/>
+      <c r="H7" s="221"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="90">
@@ -8244,7 +8209,7 @@
       <c r="G8" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="222"/>
+      <c r="H8" s="221"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="90">
@@ -8268,7 +8233,7 @@
       <c r="G9" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="222"/>
+      <c r="H9" s="221"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="90">
@@ -8292,7 +8257,7 @@
       <c r="G10" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="222"/>
+      <c r="H10" s="221"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="90">
@@ -8316,7 +8281,7 @@
       <c r="G11" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H11" s="222"/>
+      <c r="H11" s="221"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="90">
@@ -8340,7 +8305,7 @@
       <c r="G12" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="222"/>
+      <c r="H12" s="221"/>
     </row>
     <row r="13" spans="1:8" ht="60.75">
       <c r="A13" s="90">
@@ -8364,7 +8329,7 @@
       <c r="G13" s="91" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="222"/>
+      <c r="H13" s="221"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="90">
@@ -8388,7 +8353,7 @@
       <c r="G14" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="222"/>
+      <c r="H14" s="221"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="90">
@@ -8412,7 +8377,7 @@
       <c r="G15" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="222"/>
+      <c r="H15" s="221"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="90">
@@ -8436,7 +8401,7 @@
       <c r="G16" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="222"/>
+      <c r="H16" s="221"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="90">
@@ -8460,7 +8425,7 @@
       <c r="G17" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="222"/>
+      <c r="H17" s="221"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="90">
@@ -8484,7 +8449,7 @@
       <c r="G18" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H18" s="222"/>
+      <c r="H18" s="221"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="90">
@@ -8508,7 +8473,7 @@
       <c r="G19" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="222"/>
+      <c r="H19" s="221"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="90">
@@ -8532,7 +8497,7 @@
       <c r="G20" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H20" s="222"/>
+      <c r="H20" s="221"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="90">
@@ -8556,7 +8521,7 @@
       <c r="G21" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H21" s="222"/>
+      <c r="H21" s="221"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="90">
@@ -8580,7 +8545,7 @@
       <c r="G22" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H22" s="222"/>
+      <c r="H22" s="221"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="90">
@@ -8604,7 +8569,7 @@
       <c r="G23" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H23" s="222"/>
+      <c r="H23" s="221"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="90">
@@ -8628,7 +8593,7 @@
       <c r="G24" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H24" s="222"/>
+      <c r="H24" s="221"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="90">
@@ -8652,7 +8617,7 @@
       <c r="G25" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H25" s="222"/>
+      <c r="H25" s="221"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="90">
@@ -8676,7 +8641,7 @@
       <c r="G26" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H26" s="222"/>
+      <c r="H26" s="221"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="90">
@@ -8700,7 +8665,7 @@
       <c r="G27" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H27" s="222"/>
+      <c r="H27" s="221"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="90">
@@ -8724,7 +8689,7 @@
       <c r="G28" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H28" s="222"/>
+      <c r="H28" s="221"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="90">
@@ -8748,7 +8713,7 @@
       <c r="G29" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H29" s="222"/>
+      <c r="H29" s="221"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="90">
@@ -8772,7 +8737,7 @@
       <c r="G30" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H30" s="222"/>
+      <c r="H30" s="221"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="90">
@@ -8796,7 +8761,7 @@
       <c r="G31" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H31" s="222"/>
+      <c r="H31" s="221"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="90">
@@ -8820,7 +8785,7 @@
       <c r="G32" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H32" s="222"/>
+      <c r="H32" s="221"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="90">
@@ -8844,7 +8809,7 @@
       <c r="G33" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H33" s="222"/>
+      <c r="H33" s="221"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="90">
@@ -8868,7 +8833,7 @@
       <c r="G34" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H34" s="222"/>
+      <c r="H34" s="221"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="90">
@@ -8892,7 +8857,7 @@
       <c r="G35" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H35" s="222"/>
+      <c r="H35" s="221"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="90">
@@ -8916,7 +8881,7 @@
       <c r="G36" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H36" s="222"/>
+      <c r="H36" s="221"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="90">
@@ -8940,7 +8905,7 @@
       <c r="G37" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H37" s="222"/>
+      <c r="H37" s="221"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="90">
@@ -8964,7 +8929,7 @@
       <c r="G38" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H38" s="222"/>
+      <c r="H38" s="221"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="90">
@@ -8988,7 +8953,7 @@
       <c r="G39" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H39" s="222"/>
+      <c r="H39" s="221"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="90">
@@ -9012,7 +8977,7 @@
       <c r="G40" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H40" s="222"/>
+      <c r="H40" s="221"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="90">
@@ -9036,7 +9001,7 @@
       <c r="G41" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H41" s="222"/>
+      <c r="H41" s="221"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="90">
@@ -9060,7 +9025,7 @@
       <c r="G42" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H42" s="222"/>
+      <c r="H42" s="221"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="90">
@@ -9084,7 +9049,7 @@
       <c r="G43" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H43" s="222"/>
+      <c r="H43" s="221"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="90">
@@ -9108,7 +9073,7 @@
       <c r="G44" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H44" s="222"/>
+      <c r="H44" s="221"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="90">
@@ -9132,7 +9097,7 @@
       <c r="G45" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H45" s="222"/>
+      <c r="H45" s="221"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="90">
@@ -9156,7 +9121,7 @@
       <c r="G46" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H46" s="222"/>
+      <c r="H46" s="221"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="90">
@@ -9180,7 +9145,7 @@
       <c r="G47" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H47" s="222"/>
+      <c r="H47" s="221"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="90">
@@ -9204,7 +9169,7 @@
       <c r="G48" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H48" s="222"/>
+      <c r="H48" s="221"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="90">
@@ -9228,7 +9193,7 @@
       <c r="G49" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H49" s="222"/>
+      <c r="H49" s="221"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="90">
@@ -9252,7 +9217,7 @@
       <c r="G50" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H50" s="222"/>
+      <c r="H50" s="221"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="90">
@@ -9276,7 +9241,7 @@
       <c r="G51" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H51" s="222"/>
+      <c r="H51" s="221"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="90">
@@ -9300,7 +9265,7 @@
       <c r="G52" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H52" s="222"/>
+      <c r="H52" s="221"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="90">
@@ -9324,7 +9289,7 @@
       <c r="G53" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H53" s="222"/>
+      <c r="H53" s="221"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="90">
@@ -9348,7 +9313,7 @@
       <c r="G54" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H54" s="222"/>
+      <c r="H54" s="221"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="90">
@@ -9372,7 +9337,7 @@
       <c r="G55" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H55" s="222"/>
+      <c r="H55" s="221"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="90">
@@ -9396,7 +9361,7 @@
       <c r="G56" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H56" s="222"/>
+      <c r="H56" s="221"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="90">
@@ -9420,7 +9385,7 @@
       <c r="G57" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="H57" s="222"/>
+      <c r="H57" s="221"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="114">
@@ -9444,137 +9409,137 @@
       <c r="G58" s="115" t="s">
         <v>46</v>
       </c>
-      <c r="H58" s="222"/>
+      <c r="H58" s="221"/>
     </row>
     <row r="59" spans="1:8">
-      <c r="A59" s="223">
+      <c r="A59" s="222">
         <v>53</v>
       </c>
-      <c r="B59" s="220" t="s">
+      <c r="B59" s="219" t="s">
         <v>41</v>
       </c>
-      <c r="C59" s="224" t="s">
+      <c r="C59" s="223" t="s">
         <v>154</v>
       </c>
-      <c r="D59" s="225" t="s">
+      <c r="D59" s="224" t="s">
         <v>43</v>
       </c>
-      <c r="E59" s="226" t="s">
-        <v>44</v>
-      </c>
-      <c r="F59" s="220" t="s">
+      <c r="E59" s="225" t="s">
+        <v>44</v>
+      </c>
+      <c r="F59" s="219" t="s">
         <v>155</v>
       </c>
-      <c r="G59" s="220" t="s">
+      <c r="G59" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="H59" s="222"/>
+      <c r="H59" s="221"/>
     </row>
     <row r="60" spans="1:8">
-      <c r="A60" s="223">
+      <c r="A60" s="222">
         <v>54</v>
       </c>
-      <c r="B60" s="220" t="s">
+      <c r="B60" s="219" t="s">
         <v>41</v>
       </c>
-      <c r="C60" s="224" t="s">
+      <c r="C60" s="223" t="s">
         <v>156</v>
       </c>
-      <c r="D60" s="225" t="s">
+      <c r="D60" s="224" t="s">
         <v>43</v>
       </c>
-      <c r="E60" s="226" t="s">
-        <v>44</v>
-      </c>
-      <c r="F60" s="220" t="s">
+      <c r="E60" s="225" t="s">
+        <v>44</v>
+      </c>
+      <c r="F60" s="219" t="s">
         <v>157</v>
       </c>
-      <c r="G60" s="220" t="s">
+      <c r="G60" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="H60" s="222"/>
+      <c r="H60" s="221"/>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="223">
+      <c r="A61" s="222">
         <v>55</v>
       </c>
-      <c r="B61" s="220" t="s">
+      <c r="B61" s="219" t="s">
         <v>41</v>
       </c>
-      <c r="C61" s="224" t="s">
+      <c r="C61" s="223" t="s">
         <v>158</v>
       </c>
-      <c r="D61" s="225" t="s">
+      <c r="D61" s="224" t="s">
         <v>43</v>
       </c>
-      <c r="E61" s="226" t="s">
-        <v>44</v>
-      </c>
-      <c r="F61" s="220" t="s">
+      <c r="E61" s="225" t="s">
+        <v>44</v>
+      </c>
+      <c r="F61" s="219" t="s">
         <v>159</v>
       </c>
-      <c r="G61" s="220" t="s">
+      <c r="G61" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="H61" s="222"/>
+      <c r="H61" s="221"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="223">
+      <c r="A62" s="222">
         <v>56</v>
       </c>
-      <c r="B62" s="220" t="s">
+      <c r="B62" s="219" t="s">
         <v>41</v>
       </c>
-      <c r="C62" s="224" t="s">
+      <c r="C62" s="223" t="s">
         <v>160</v>
       </c>
-      <c r="D62" s="225" t="s">
+      <c r="D62" s="224" t="s">
         <v>76</v>
       </c>
-      <c r="E62" s="226" t="s">
-        <v>44</v>
-      </c>
-      <c r="F62" s="220" t="s">
+      <c r="E62" s="225" t="s">
+        <v>44</v>
+      </c>
+      <c r="F62" s="219" t="s">
         <v>161</v>
       </c>
-      <c r="G62" s="220" t="s">
+      <c r="G62" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="H62" s="222"/>
+      <c r="H62" s="221"/>
     </row>
     <row r="63" spans="1:8">
-      <c r="A63" s="223">
+      <c r="A63" s="222">
         <v>57</v>
       </c>
-      <c r="B63" s="220" t="s">
+      <c r="B63" s="219" t="s">
         <v>41</v>
       </c>
-      <c r="C63" s="224" t="s">
+      <c r="C63" s="223" t="s">
         <v>162</v>
       </c>
-      <c r="D63" s="225" t="s">
+      <c r="D63" s="224" t="s">
         <v>43</v>
       </c>
-      <c r="E63" s="226" t="s">
-        <v>44</v>
-      </c>
-      <c r="F63" s="220" t="s">
+      <c r="E63" s="225" t="s">
+        <v>44</v>
+      </c>
+      <c r="F63" s="219" t="s">
         <v>163</v>
       </c>
-      <c r="G63" s="220" t="s">
+      <c r="G63" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="H63" s="222"/>
+      <c r="H63" s="221"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="227"/>
-      <c r="B64" s="222"/>
-      <c r="C64" s="227"/>
-      <c r="D64" s="227"/>
-      <c r="E64" s="222"/>
-      <c r="F64" s="222"/>
-      <c r="G64" s="222"/>
-      <c r="H64" s="228"/>
+      <c r="A64" s="226"/>
+      <c r="B64" s="221"/>
+      <c r="C64" s="226"/>
+      <c r="D64" s="226"/>
+      <c r="E64" s="221"/>
+      <c r="F64" s="221"/>
+      <c r="G64" s="221"/>
+      <c r="H64" s="227"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9602,14 +9567,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="157" t="s">
+      <c r="A1" s="167" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="158"/>
-      <c r="C1" s="158"/>
-      <c r="D1" s="158"/>
-      <c r="E1" s="158"/>
-      <c r="F1" s="158"/>
+      <c r="B1" s="168"/>
+      <c r="C1" s="168"/>
+      <c r="D1" s="168"/>
+      <c r="E1" s="168"/>
+      <c r="F1" s="168"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7">
@@ -9619,10 +9584,10 @@
       <c r="B2" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="159" t="s">
+      <c r="C2" s="169" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="160"/>
+      <c r="D2" s="170"/>
       <c r="E2" s="40" t="s">
         <v>25</v>
       </c>
@@ -9638,10 +9603,10 @@
       <c r="B3" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="C3" s="161" t="s">
+      <c r="C3" s="171" t="s">
         <v>166</v>
       </c>
-      <c r="D3" s="162"/>
+      <c r="D3" s="172"/>
       <c r="E3" s="41" t="s">
         <v>29</v>
       </c>
@@ -9657,10 +9622,10 @@
       <c r="B4" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="161" t="s">
+      <c r="C4" s="171" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="162"/>
+      <c r="D4" s="172"/>
       <c r="E4" s="41" t="s">
         <v>32</v>
       </c>
@@ -9669,14 +9634,14 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="168" t="s">
         <v>170</v>
       </c>
-      <c r="B5" s="158"/>
-      <c r="C5" s="158"/>
-      <c r="D5" s="158"/>
-      <c r="E5" s="158"/>
-      <c r="F5" s="158"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="168"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="40" t="s">
@@ -9806,14 +9771,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A1" s="163" t="s">
+      <c r="A1" s="173" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
-      <c r="E1" s="164"/>
-      <c r="F1" s="164"/>
+      <c r="B1" s="174"/>
+      <c r="C1" s="174"/>
+      <c r="D1" s="174"/>
+      <c r="E1" s="174"/>
+      <c r="F1" s="174"/>
     </row>
     <row r="2" spans="1:6" ht="24.75" customHeight="1">
       <c r="A2" s="46" t="s">
@@ -9822,10 +9787,10 @@
       <c r="B2" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="165" t="s">
+      <c r="C2" s="175" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="166"/>
+      <c r="D2" s="176"/>
       <c r="E2" s="46" t="s">
         <v>25</v>
       </c>
@@ -9840,10 +9805,10 @@
       <c r="B3" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="167" t="s">
+      <c r="C3" s="177" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="168"/>
+      <c r="D3" s="178"/>
       <c r="E3" s="47" t="s">
         <v>29</v>
       </c>
@@ -9856,10 +9821,10 @@
       <c r="B4" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="C4" s="169" t="s">
+      <c r="C4" s="179" t="s">
         <v>190</v>
       </c>
-      <c r="D4" s="170"/>
+      <c r="D4" s="180"/>
       <c r="E4" s="49" t="s">
         <v>191</v>
       </c>
@@ -9868,22 +9833,22 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="24.75" customHeight="1">
-      <c r="A5" s="228"/>
-      <c r="B5" s="228"/>
-      <c r="C5" s="228"/>
-      <c r="D5" s="228"/>
-      <c r="E5" s="228"/>
-      <c r="F5" s="228"/>
+      <c r="A5" s="227"/>
+      <c r="B5" s="227"/>
+      <c r="C5" s="227"/>
+      <c r="D5" s="227"/>
+      <c r="E5" s="227"/>
+      <c r="F5" s="227"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="165" t="s">
+      <c r="A7" s="175" t="s">
         <v>193</v>
       </c>
-      <c r="B7" s="171"/>
-      <c r="C7" s="171"/>
-      <c r="D7" s="171"/>
-      <c r="E7" s="171"/>
-      <c r="F7" s="228"/>
+      <c r="B7" s="181"/>
+      <c r="C7" s="181"/>
+      <c r="D7" s="181"/>
+      <c r="E7" s="181"/>
+      <c r="F7" s="227"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="46" t="s">
@@ -9901,7 +9866,7 @@
       <c r="E8" s="46" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="228"/>
+      <c r="F8" s="227"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="51" t="s">
@@ -9919,7 +9884,7 @@
       <c r="E9" s="54" t="s">
         <v>195</v>
       </c>
-      <c r="F9" s="228"/>
+      <c r="F9" s="227"/>
     </row>
     <row r="10" spans="1:6" ht="60.75">
       <c r="A10" s="51" t="s">
@@ -9937,7 +9902,7 @@
       <c r="E10" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="F10" s="228"/>
+      <c r="F10" s="227"/>
     </row>
     <row r="11" spans="1:6" ht="91.5">
       <c r="A11" s="51" t="s">
@@ -9955,7 +9920,7 @@
       <c r="E11" s="54" t="s">
         <v>200</v>
       </c>
-      <c r="F11" s="228"/>
+      <c r="F11" s="227"/>
     </row>
     <row r="12" spans="1:6" ht="121.5">
       <c r="A12" s="51" t="s">
@@ -9973,7 +9938,7 @@
       <c r="E12" s="54" t="s">
         <v>203</v>
       </c>
-      <c r="F12" s="228"/>
+      <c r="F12" s="227"/>
     </row>
     <row r="13" spans="1:6" ht="76.5">
       <c r="A13" s="51" t="s">
@@ -9991,7 +9956,7 @@
       <c r="E13" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="F13" s="228"/>
+      <c r="F13" s="227"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="51" t="s">
@@ -10009,7 +9974,7 @@
       <c r="E14" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="F14" s="228"/>
+      <c r="F14" s="227"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="51" t="s">
@@ -10027,7 +9992,7 @@
       <c r="E15" s="54" t="s">
         <v>210</v>
       </c>
-      <c r="F15" s="228"/>
+      <c r="F15" s="227"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -10054,13 +10019,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="174" t="s">
+      <c r="A1" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="176"/>
+      <c r="B1" s="185"/>
+      <c r="C1" s="185"/>
+      <c r="D1" s="185"/>
+      <c r="E1" s="186"/>
       <c r="F1" s="5"/>
     </row>
     <row r="2" spans="1:6">
@@ -10161,39 +10126,39 @@
       <c r="E7" s="30"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1">
-      <c r="A8" s="174" t="s">
+      <c r="A8" s="184" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="175"/>
-      <c r="C8" s="175"/>
-      <c r="D8" s="175"/>
-      <c r="E8" s="175"/>
+      <c r="B8" s="185"/>
+      <c r="C8" s="185"/>
+      <c r="D8" s="185"/>
+      <c r="E8" s="185"/>
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="177" t="s">
+      <c r="A9" s="187" t="s">
         <v>221</v>
       </c>
-      <c r="B9" s="178" t="s">
+      <c r="B9" s="188" t="s">
         <v>222</v>
       </c>
-      <c r="C9" s="178" t="s">
+      <c r="C9" s="188" t="s">
         <v>173</v>
       </c>
-      <c r="D9" s="179" t="s">
+      <c r="D9" s="189" t="s">
         <v>174</v>
       </c>
-      <c r="E9" s="179" t="s">
+      <c r="E9" s="189" t="s">
         <v>223</v>
       </c>
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="177"/>
-      <c r="B10" s="178"/>
-      <c r="C10" s="178"/>
-      <c r="D10" s="180"/>
-      <c r="E10" s="180"/>
+      <c r="A10" s="187"/>
+      <c r="B10" s="188"/>
+      <c r="C10" s="188"/>
+      <c r="D10" s="190"/>
+      <c r="E10" s="190"/>
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:6">
@@ -11223,13 +11188,13 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="172" t="s">
+      <c r="A68" s="182" t="s">
         <v>240</v>
       </c>
-      <c r="B68" s="173"/>
-      <c r="C68" s="173"/>
-      <c r="D68" s="173"/>
-      <c r="E68" s="173"/>
+      <c r="B68" s="183"/>
+      <c r="C68" s="183"/>
+      <c r="D68" s="183"/>
+      <c r="E68" s="183"/>
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6">
@@ -12278,13 +12243,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="191" t="s">
         <v>269</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="183"/>
+      <c r="B1" s="192"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="193"/>
       <c r="F1" s="37"/>
     </row>
     <row r="2" spans="1:6">
@@ -12331,13 +12296,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="184" t="s">
+      <c r="A5" s="194" t="s">
         <v>272</v>
       </c>
-      <c r="B5" s="184"/>
-      <c r="C5" s="184"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="184"/>
+      <c r="B5" s="194"/>
+      <c r="C5" s="194"/>
+      <c r="D5" s="194"/>
+      <c r="E5" s="194"/>
       <c r="F5" s="106"/>
     </row>
     <row r="6" spans="1:6">
@@ -12520,13 +12485,13 @@
       <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="185" t="s">
+      <c r="A5" s="195" t="s">
         <v>220</v>
       </c>
-      <c r="B5" s="185"/>
-      <c r="C5" s="185"/>
-      <c r="D5" s="185"/>
-      <c r="E5" s="185"/>
+      <c r="B5" s="195"/>
+      <c r="C5" s="195"/>
+      <c r="D5" s="195"/>
+      <c r="E5" s="195"/>
     </row>
     <row r="6" spans="1:5" ht="24.75">
       <c r="A6" s="21" t="s">
@@ -12714,8 +12679,8 @@
       </c>
       <c r="B6" s="58"/>
       <c r="C6" s="58"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
+      <c r="D6" s="198"/>
+      <c r="E6" s="198"/>
       <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="21" customHeight="1">
@@ -12728,10 +12693,10 @@
       <c r="C7" s="59" t="s">
         <v>173</v>
       </c>
-      <c r="D7" s="189" t="s">
+      <c r="D7" s="199" t="s">
         <v>174</v>
       </c>
-      <c r="E7" s="190"/>
+      <c r="E7" s="200"/>
       <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" ht="21" customHeight="1">
@@ -12744,10 +12709,10 @@
       <c r="C8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="186" t="s">
+      <c r="D8" s="196" t="s">
         <v>298</v>
       </c>
-      <c r="E8" s="187"/>
+      <c r="E8" s="197"/>
       <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" ht="21" customHeight="1">
@@ -12760,10 +12725,10 @@
       <c r="C9" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="186" t="s">
+      <c r="D9" s="196" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="187"/>
+      <c r="E9" s="197"/>
       <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="14.45" customHeight="1">
@@ -12776,10 +12741,10 @@
       <c r="C10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="186" t="s">
+      <c r="D10" s="196" t="s">
         <v>96</v>
       </c>
-      <c r="E10" s="187"/>
+      <c r="E10" s="197"/>
     </row>
     <row r="11" spans="1:7" ht="14.45" customHeight="1">
       <c r="A11" s="8" t="s">
@@ -12791,10 +12756,10 @@
       <c r="C11" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="186" t="s">
+      <c r="D11" s="196" t="s">
         <v>98</v>
       </c>
-      <c r="E11" s="187"/>
+      <c r="E11" s="197"/>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1">
       <c r="A12" s="8" t="s">
@@ -12806,10 +12771,10 @@
       <c r="C12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="186" t="s">
+      <c r="D12" s="196" t="s">
         <v>300</v>
       </c>
-      <c r="E12" s="187"/>
+      <c r="E12" s="197"/>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1">
       <c r="A13" s="8" t="s">
@@ -12821,10 +12786,10 @@
       <c r="C13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="186" t="s">
+      <c r="D13" s="196" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="187"/>
+      <c r="E13" s="197"/>
     </row>
     <row r="14" spans="1:7" ht="70.5" customHeight="1">
       <c r="A14" s="8" t="s">
@@ -12836,10 +12801,10 @@
       <c r="C14" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D14" s="186" t="s">
+      <c r="D14" s="196" t="s">
         <v>302</v>
       </c>
-      <c r="E14" s="187"/>
+      <c r="E14" s="197"/>
     </row>
     <row r="15" spans="1:7" ht="14.45" customHeight="1"/>
   </sheetData>
@@ -12859,16 +12824,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -13040,6 +12995,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -13050,11 +13015,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/input/mapping/064. OCB_GOLD_TCKH_CST_DIM_NEW_HOP.xlsx
+++ b/input/mapping/064. OCB_GOLD_TCKH_CST_DIM_NEW_HOP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30408"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/KHTC - Phân tích/06. Mapping View Layer 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1977" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC4D5DF5-9E36-4EF7-8D1E-1CF981DCB67F}"/>
+  <xr:revisionPtr revIDLastSave="1979" documentId="13_ncr:1_{585C96AB-DB4C-4D9B-A520-A2AFB1E1A13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{261F300D-CAD9-4AD6-9230-3B7CE3499682}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="798" firstSheet="15" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -235,49 +235,9 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
--- =============================================================================
--- CST_DIM_NEW  (Snapshot daily -&gt; INSERT REPLACE WHERE DATA_DT, idempotent)
--- Nguồn: Silver (hub_customer, sts_hub_customer, sat_customer_*)
--- Params: :cleaned, :curated, :DATADT (yyyyMMdd)
--- Fix:
---   2.4  : sat_customer_contact dùng &lt;= :DATADT (không phải = :DATADT)
---   2.12 : sat_customer_contact snapshot 1 lần duy nhất -&gt; cte_contact
---   X.11 : bỏ email_type_id / address_type_id / end_date (không tồn tại trong model)
--- Trace DSX:
---   ELC_ADR   = sat_customer_contact.email_1  (T24: T_EMAIL_1)
---   CST_ADR   = sat_customer_contact.add_num  (T24: T_ADD_NUM)
---   CST_FAX_NO= sat_customer_other.fax_1      (T24: T_FAX_1)
---   CST_MBL_NO= NULL  (on-prem set_null())
---   INN_BNKG_F= NULL  (on-prem set_null())
--- =============================================================================
-CREATE TABLE IF NOT EXISTS CST_DIM_NEW (
-    DATA_DT            DATE,
-    CST_DW_ID          STRING,
-    UNQ_ID_SRC_STM     STRING,
-    IP_NM              STRING,
-    IP_FULL_NM         STRING,
-    BRTH_DT            DATE,
-    IDENTN_NO          STRING,
-    ORG_TAX_ID_NO      STRING,
-    ORG_TDG_LICENSE_ID STRING,
-    IDENTN_ISSU_DT     DATE,
-    GND_ID             STRING,
-    CST_GRP_ID         STRING,
-    CST_LCS_TP_ID      STRING,
-    EFF_CST_DT         DATE,
-    CST_ADR            STRING,
-    ELC_ADR            STRING,
-    CST_FAX_NO         STRING,
-    CST_MBL_NO         STRING,
-    INN_BNKG_F         STRING,
-    CRT_TM             TIMESTAMP,
-    PPN_TM             TIMESTAMP
-)
-USING DELTA;
 INSERT INTO CST_DIM_NEW
 REPLACE WHERE DATA_DT = TO_DATE(:DATADT, 'yyyyMMdd')
 WITH
--- ── STS Hub: loại customer có trạng thái mới nhất = 'D' đến :DATADT
 sts_deleted AS (
     SELECT customer_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_customer')
@@ -285,16 +245,12 @@
     GROUP BY customer_hashkey
     HAVING MAX_BY(cdc_status, source_event_date) = 'D'
 ),
--- ── Hub customer active
 cust_active AS (
     SELECT h.customer_hashkey, h.business_key
     FROM IDENTIFIER(:cleaned || '.raw_vault.hub_customer') h
     LEFT JOIN sts_deleted d ON h.customer_hashkey = d.customer_hashkey
     WHERE d.customer_hashkey IS NULL
 ),
--- ── sat_customer_contact: snapshot 1 lần (fix 2.12), dùng &lt;= :DATADT (fix 2.4)
---    Cột dùng: email_1-&gt;ELC_ADR, add_num-&gt;CST_ADR (fix X.11: bỏ email_type_id/address_type_id/end_date)
---    CST_MBL_NO không lấy sms_1 vì on-prem set_null()
 cte_contact AS (
     SELECT
         customer_hashkey,
@@ -304,7 +260,6 @@
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
 ),
--- ── Satellite information (bản mới nhất &lt;= :DATADT)
 sat_info AS (
     SELECT
         customer_hashkey,
@@ -317,7 +272,6 @@
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
 ),
--- ── Satellite KYC (bản mới nhất &lt;= :DATADT)
 sat_kyc AS (
     SELECT
         customer_hashkey,
@@ -329,7 +283,6 @@
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
 ),
--- ── Satellite classification (bản mới nhất &lt;= :DATADT)
 sat_cls AS (
     SELECT
         customer_hashkey,
@@ -339,7 +292,6 @@
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
 ),
--- ── Satellite other: fax_1-&gt;CST_FAX_NO (T24: T_FAX_1, bản mới nhất &lt;= :DATADT)
 sat_other AS (
     SELECT
         customer_hashkey,
@@ -375,8 +327,7 @@
 LEFT JOIN sat_kyc     k  ON h.customer_hashkey = k.customer_hashkey
 LEFT JOIN sat_cls     c  ON h.customer_hashkey = c.customer_hashkey
 LEFT JOIN cte_contact ct ON h.customer_hashkey = ct.customer_hashkey
-LEFT JOIN sat_other   o  ON h.customer_hashkey = o.customer_hashkey
-;</t>
+LEFT JOIN sat_other   o  ON h.customer_hashkey = o.customer_hashkey</t>
   </si>
   <si>
     <t>JOIN SCHEMA</t>
@@ -3266,9 +3217,7 @@
       <alignment horizontal="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -8025,7 +7974,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="409.6">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -12824,6 +12773,16 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -12995,16 +12954,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -13015,11 +12964,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{338796C8-1E45-4AA1-BD60-A388396432A2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7AEAC08E-CA6D-43CF-BD5D-30D3E42B8B9C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
